--- a/data/shiny_functions.xlsx
+++ b/data/shiny_functions.xlsx
@@ -1,16 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\araya\Documents\R入門\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41D24882-FCF8-4146-8902-58224D15A440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E272CE07-0FF9-450D-B9E6-2257313B6359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{08960AF4-DAE1-4BF8-96BF-FAA9FE1A6FAC}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="16440" activeTab="3" xr2:uid="{08960AF4-DAE1-4BF8-96BF-FAA9FE1A6FAC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1247,6 +1242,7 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1431,6 +1427,7 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1510,6 +1507,7 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1601,5 +1599,6 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>